--- a/tests/fixtures/ideal_input/rate_schedule.xlsx
+++ b/tests/fixtures/ideal_input/rate_schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL11"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,406 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100008</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100009</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="X13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
         <v>0</v>
       </c>
     </row>
